--- a/output/THONGKE_ca1.XLSX
+++ b/output/THONGKE_ca1.XLSX
@@ -133,7 +133,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -145,7 +145,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -193,7 +193,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>192</t>
         </is>
       </c>
     </row>
@@ -205,7 +205,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
